--- a/results/models/coverage_v5_SA_PROMETHEE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
+++ b/results/models/coverage_v5_SA_PROMETHEE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
@@ -448,10 +448,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.631610092420439</v>
+        <v>2.112027978662345</v>
       </c>
       <c r="D2" t="n">
-        <v>3.631610092420439</v>
+        <v>2.112027978662345</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3.949421663599871</v>
+        <v>5.525357952703625</v>
       </c>
       <c r="D3" t="n">
-        <v>3.949421663599871</v>
+        <v>5.525357952703625</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3.871215688363641</v>
+        <v>5.223476349180064</v>
       </c>
       <c r="D4" t="n">
-        <v>3.871215688363641</v>
+        <v>5.223476349180064</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2.825930286551192</v>
+        <v>2.971243140865348</v>
       </c>
       <c r="D5" t="n">
-        <v>2.825930286551192</v>
+        <v>2.971243140865348</v>
       </c>
     </row>
     <row r="6">
@@ -512,10 +512,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3.273066064871467</v>
+        <v>5.178424164819851</v>
       </c>
       <c r="D6" t="n">
-        <v>3.273066064871467</v>
+        <v>5.178424164819851</v>
       </c>
     </row>
     <row r="7">
@@ -528,10 +528,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>6.064350700846656</v>
+        <v>5.716267200807207</v>
       </c>
       <c r="D7" t="n">
-        <v>6.064350700846656</v>
+        <v>5.716267200807207</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3.930267443162767</v>
+        <v>4.10896839474808</v>
       </c>
       <c r="D8" t="n">
-        <v>3.930267443162767</v>
+        <v>4.10896839474808</v>
       </c>
     </row>
     <row r="9">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4.798587608353699</v>
+        <v>4.090102714313807</v>
       </c>
       <c r="D9" t="n">
-        <v>4.798587608353699</v>
+        <v>4.090102714313807</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.935726659309648</v>
+        <v>2.113653559235216</v>
       </c>
       <c r="D10" t="n">
-        <v>1.935726659309648</v>
+        <v>2.113653559235216</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5.386242240380523</v>
+        <v>4.03221689714431</v>
       </c>
       <c r="D11" t="n">
-        <v>5.386242240380523</v>
+        <v>4.03221689714431</v>
       </c>
     </row>
     <row r="12">
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.477803046473058</v>
+        <v>1.951133505460507</v>
       </c>
       <c r="D12" t="n">
-        <v>1.477803046473058</v>
+        <v>1.951133505460507</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.047319129032931</v>
+        <v>3.172850584040361</v>
       </c>
       <c r="D14" t="n">
-        <v>3.047319129032931</v>
+        <v>3.172850584040361</v>
       </c>
     </row>
     <row r="15">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>5.485654278560254</v>
+        <v>6.176844796570573</v>
       </c>
       <c r="D15" t="n">
-        <v>5.485654278560254</v>
+        <v>6.176844796570573</v>
       </c>
     </row>
     <row r="16">
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>4.213237291998356</v>
+        <v>4.005330360362547</v>
       </c>
       <c r="D16" t="n">
-        <v>4.213237291998356</v>
+        <v>4.005330360362547</v>
       </c>
     </row>
   </sheetData>
